--- a/04_Figures/F4/c_data/F4.xlsx
+++ b/04_Figures/F4/c_data/F4.xlsx
@@ -170,7 +170,7 @@
     <t>label</t>
   </si>
   <si>
-    <t>Set name as printed in the figure; * marks calls of opposite sign within the window.</t>
+    <t>Set name as printed in the figure; * marks calls of opposite sign within the window; † a training or acute set whose interaction also reaches FDR &lt; 0.05.</t>
   </si>
   <si>
     <t>nes</t>
@@ -659,7 +659,7 @@
     <t>Reactome|REACTOME_ASPARAGINE_N_LINKED_GLYCOSYLATION</t>
   </si>
   <si>
-    <t>Asparagine n linked glycosylation</t>
+    <t>Asparagine N linked glycosylation</t>
   </si>
   <si>
     <t>Reactome|REACTOME_CELLULAR_SENESCENCE</t>

--- a/04_Figures/F4/c_data/F4.xlsx
+++ b/04_Figures/F4/c_data/F4.xlsx
@@ -521,7 +521,7 @@
     <t>Reactome|REACTOME_AEROBIC_RESPIRATION_AND_RESPIRATORY_ELECTRON_TRANSPORT</t>
   </si>
   <si>
-    <t>Aerobic respiration and respiratory electron tran...</t>
+    <t>Aerobic respiration and respiratory electron transport</t>
   </si>
   <si>
     <t>GOBP|GOBP_TRICARBOXYLIC_ACID_CYCLE</t>
@@ -629,13 +629,13 @@
     <t>GOBP|GOBP_REGULATION_OF_ESTABLISHMENT_OF_PROTEIN_LOCALIZATION_TO_MITOCHONDRION</t>
   </si>
   <si>
-    <t>Regulation of establishment of protein localizati...</t>
+    <t>Regulation of establishment of protein localization to mitoch...</t>
   </si>
   <si>
     <t>GOBP|GOBP_POSITIVE_REGULATION_OF_PROTEIN_LOCALIZATION_TO_CELL_PERIPHERY</t>
   </si>
   <si>
-    <t>Positive regulation of protein localization to ce...</t>
+    <t>Positive regulation of protein localization to cell periphery</t>
   </si>
   <si>
     <t>Reactome|REACTOME_EPIGENETIC_REGULATION_OF_GENE_EXPRESSION</t>
@@ -671,7 +671,7 @@
     <t>GOBP|GOBP_ENDOPLASMIC_RETICULUM_TO_GOLGI_VESICLE_MEDIATED_TRANSPORT</t>
   </si>
   <si>
-    <t>Endoplasmic reticulum to Golgi vesicle mediated t...</t>
+    <t>Endoplasmic reticulum to Golgi vesicle mediated transport</t>
   </si>
   <si>
     <t>GOBP|GOBP_STRIATED_MUSCLE_ADAPTATION</t>
@@ -689,7 +689,7 @@
     <t>GOBP|GOBP_NEGATIVE_REGULATION_OF_SYNCYTIUM_FORMATION_BY_PLASMA_MEMBRANE_FUSION</t>
   </si>
   <si>
-    <t>Negative regulation of syncytium formation by pla...</t>
+    <t>Negative regulation of syncytium formation by plasma membrane...</t>
   </si>
   <si>
     <t>Reactome|REACTOME_RHO_GTPASES_ACTIVATE_PKNS</t>

--- a/04_Figures/F4/c_data/F4.xlsx
+++ b/04_Figures/F4/c_data/F4.xlsx
@@ -697,7 +697,7 @@
     <t>03_Continuous/01_Trait_Associations/c_data/associations.rds</t>
   </si>
   <si>
-    <t>106dbce514663d88a855197663b842c8</t>
+    <t>bcc122524b1e4253791773a6fe889a66</t>
   </si>
   <si>
     <t>trait_pathways</t>
@@ -6131,13 +6131,13 @@
         <v>95</v>
       </c>
       <c r="D86">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E86">
         <v>0</v>
       </c>
       <c r="F86">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -6157,13 +6157,13 @@
         <v>96</v>
       </c>
       <c r="D87">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E87">
         <v>0</v>
       </c>
       <c r="F87">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -6183,19 +6183,19 @@
         <v>97</v>
       </c>
       <c r="D88">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F88">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G88">
         <v>0</v>
       </c>
       <c r="H88">
-        <v>0.07692307692307693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:8">
@@ -6209,13 +6209,13 @@
         <v>98</v>
       </c>
       <c r="D89">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
       <c r="F89">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -6235,19 +6235,19 @@
         <v>99</v>
       </c>
       <c r="D90">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E90">
         <v>1</v>
       </c>
       <c r="F90">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G90">
         <v>0</v>
       </c>
       <c r="H90">
-        <v>0.07692307692307693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="91" spans="1:8">
@@ -6261,19 +6261,19 @@
         <v>100</v>
       </c>
       <c r="D91">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F91">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G91">
         <v>0</v>
       </c>
       <c r="H91">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="92" spans="1:8">
@@ -6287,13 +6287,13 @@
         <v>66</v>
       </c>
       <c r="D92">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -6313,13 +6313,13 @@
         <v>68</v>
       </c>
       <c r="D93">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -6339,13 +6339,13 @@
         <v>69</v>
       </c>
       <c r="D94">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -6365,13 +6365,13 @@
         <v>70</v>
       </c>
       <c r="D95">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E95">
         <v>0</v>
       </c>
       <c r="F95">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G95">
         <v>0</v>
@@ -6391,19 +6391,19 @@
         <v>71</v>
       </c>
       <c r="D96">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F96">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G96">
         <v>0</v>
       </c>
       <c r="H96">
-        <v>0.1538461538461539</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="97" spans="1:8">
@@ -6417,13 +6417,13 @@
         <v>72</v>
       </c>
       <c r="D97">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -6443,13 +6443,13 @@
         <v>73</v>
       </c>
       <c r="D98">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E98">
         <v>0</v>
       </c>
       <c r="F98">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -6469,19 +6469,19 @@
         <v>75</v>
       </c>
       <c r="D99">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E99">
         <v>1</v>
       </c>
       <c r="F99">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G99">
         <v>0</v>
       </c>
       <c r="H99">
-        <v>0.07692307692307693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="100" spans="1:8">
@@ -6495,13 +6495,13 @@
         <v>66</v>
       </c>
       <c r="D100">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -6521,13 +6521,13 @@
         <v>68</v>
       </c>
       <c r="D101">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G101">
         <v>0</v>
@@ -6547,19 +6547,19 @@
         <v>69</v>
       </c>
       <c r="D102">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F102">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G102">
         <v>0</v>
       </c>
       <c r="H102">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="103" spans="1:8">
@@ -6573,19 +6573,19 @@
         <v>70</v>
       </c>
       <c r="D103">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E103">
         <v>2</v>
       </c>
       <c r="F103">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G103">
         <v>0</v>
       </c>
       <c r="H103">
-        <v>0.1538461538461539</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="104" spans="1:8">
@@ -6599,19 +6599,19 @@
         <v>71</v>
       </c>
       <c r="D104">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E104">
         <v>1</v>
       </c>
       <c r="F104">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G104">
         <v>0</v>
       </c>
       <c r="H104">
-        <v>0.07692307692307693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -6625,13 +6625,13 @@
         <v>72</v>
       </c>
       <c r="D105">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E105">
         <v>0</v>
       </c>
       <c r="F105">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -6651,19 +6651,19 @@
         <v>73</v>
       </c>
       <c r="D106">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E106">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F106">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G106">
         <v>0</v>
       </c>
       <c r="H106">
-        <v>0.07692307692307693</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:8">
@@ -6677,19 +6677,19 @@
         <v>75</v>
       </c>
       <c r="D107">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F107">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G107">
         <v>0</v>
       </c>
       <c r="H107">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -6703,13 +6703,13 @@
         <v>95</v>
       </c>
       <c r="D108">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E108">
         <v>0</v>
       </c>
       <c r="F108">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G108">
         <v>0</v>
@@ -6729,13 +6729,13 @@
         <v>96</v>
       </c>
       <c r="D109">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E109">
         <v>0</v>
       </c>
       <c r="F109">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G109">
         <v>0</v>
@@ -6755,13 +6755,13 @@
         <v>97</v>
       </c>
       <c r="D110">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G110">
         <v>0</v>
@@ -6781,19 +6781,19 @@
         <v>98</v>
       </c>
       <c r="D111">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E111">
         <v>1</v>
       </c>
       <c r="F111">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G111">
         <v>0</v>
       </c>
       <c r="H111">
-        <v>0.07692307692307693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="112" spans="1:8">
@@ -6807,13 +6807,13 @@
         <v>99</v>
       </c>
       <c r="D112">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -6833,13 +6833,13 @@
         <v>100</v>
       </c>
       <c r="D113">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E113">
         <v>0</v>
       </c>
       <c r="F113">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G113">
         <v>0</v>
@@ -6859,19 +6859,19 @@
         <v>66</v>
       </c>
       <c r="D114">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E114">
         <v>1</v>
       </c>
       <c r="F114">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G114">
         <v>0</v>
       </c>
       <c r="H114">
-        <v>0.07692307692307693</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -6885,13 +6885,13 @@
         <v>68</v>
       </c>
       <c r="D115">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -6911,19 +6911,19 @@
         <v>69</v>
       </c>
       <c r="D116">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E116">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F116">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G116">
         <v>0</v>
       </c>
       <c r="H116">
-        <v>0.1538461538461539</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -6937,19 +6937,19 @@
         <v>70</v>
       </c>
       <c r="D117">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E117">
         <v>2</v>
       </c>
       <c r="F117">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G117">
         <v>0</v>
       </c>
       <c r="H117">
-        <v>0.1538461538461539</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="118" spans="1:8">
@@ -6963,13 +6963,13 @@
         <v>71</v>
       </c>
       <c r="D118">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E118">
         <v>0</v>
       </c>
       <c r="F118">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G118">
         <v>0</v>
@@ -6989,13 +6989,13 @@
         <v>72</v>
       </c>
       <c r="D119">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G119">
         <v>0</v>
@@ -7015,19 +7015,19 @@
         <v>73</v>
       </c>
       <c r="D120">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F120">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G120">
         <v>0</v>
       </c>
       <c r="H120">
-        <v>0.2307692307692308</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="121" spans="1:8">
@@ -7041,13 +7041,13 @@
         <v>75</v>
       </c>
       <c r="D121">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -7067,13 +7067,13 @@
         <v>95</v>
       </c>
       <c r="D122">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -7093,13 +7093,13 @@
         <v>96</v>
       </c>
       <c r="D123">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         <v>97</v>
       </c>
       <c r="D124">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -7145,13 +7145,13 @@
         <v>98</v>
       </c>
       <c r="D125">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -7171,13 +7171,13 @@
         <v>99</v>
       </c>
       <c r="D126">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -7197,13 +7197,13 @@
         <v>100</v>
       </c>
       <c r="D127">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E127">
         <v>0</v>
       </c>
       <c r="F127">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="G127">
         <v>0</v>
